--- a/Pune-June-2025.xlsx
+++ b/Pune-June-2025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="98">
   <si>
     <t>Sr. No</t>
   </si>
@@ -94,6 +94,9 @@
     <t>Profit %</t>
   </si>
   <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>Pune</t>
   </si>
   <si>
@@ -241,13 +244,13 @@
     <t>MP09AH4795</t>
   </si>
   <si>
-    <t>Crysta</t>
+    <t>CRYSTA</t>
   </si>
   <si>
     <t>INVICTO</t>
   </si>
   <si>
-    <t>EC3</t>
+    <t>CITROEN</t>
   </si>
   <si>
     <t>ETIOS</t>
@@ -256,19 +259,64 @@
     <t>DZIRE</t>
   </si>
   <si>
-    <t>DZIRE PETROL</t>
-  </si>
-  <si>
     <t>URBANIA</t>
   </si>
   <si>
-    <t>-</t>
+    <t>21/10/2022</t>
+  </si>
+  <si>
+    <t>17/10/2023</t>
+  </si>
+  <si>
+    <t>28/02/2019</t>
+  </si>
+  <si>
+    <t>18/11/2019</t>
+  </si>
+  <si>
+    <t>25/10/2021</t>
+  </si>
+  <si>
+    <t>27/02/2025</t>
+  </si>
+  <si>
+    <t>16/08/2024</t>
+  </si>
+  <si>
+    <t>29/07/2024</t>
+  </si>
+  <si>
+    <t>26/07/2024</t>
+  </si>
+  <si>
+    <t>30/09/2021</t>
+  </si>
+  <si>
+    <t>28/06/2022</t>
+  </si>
+  <si>
+    <t>13/07/2022</t>
+  </si>
+  <si>
+    <t>26/05/2023</t>
+  </si>
+  <si>
+    <t>29/11/2024</t>
+  </si>
+  <si>
+    <t>27/05/2025</t>
+  </si>
+  <si>
+    <t>24/01/2025</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -321,11 +369,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -620,10 +669,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z48"/>
+  <dimension ref="A1:AA48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -702,27 +751,30 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" spans="1:26">
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27">
       <c r="A2">
         <v>199</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>2025</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G2">
+        <v>76</v>
+      </c>
+      <c r="G2" s="2">
         <v>44686</v>
       </c>
       <c r="H2">
@@ -783,27 +835,27 @@
         <v>52.52</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:27">
       <c r="A3">
         <v>200</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>2025</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>75</v>
-      </c>
-      <c r="G3">
-        <v>44663</v>
+        <v>76</v>
+      </c>
+      <c r="G3" s="2">
+        <v>44899</v>
       </c>
       <c r="H3">
         <v>189449</v>
@@ -863,27 +915,27 @@
         <v>40.02</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:27">
       <c r="A4">
         <v>201</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>2025</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>75</v>
-      </c>
-      <c r="G4">
-        <v>44663</v>
+        <v>76</v>
+      </c>
+      <c r="G4" s="2">
+        <v>44899</v>
       </c>
       <c r="H4">
         <v>169132</v>
@@ -943,27 +995,27 @@
         <v>55.23</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:27">
       <c r="A5">
         <v>202</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5">
         <v>2025</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>75</v>
-      </c>
-      <c r="G5">
-        <v>44855</v>
+        <v>76</v>
+      </c>
+      <c r="G5" t="s">
+        <v>82</v>
       </c>
       <c r="H5">
         <v>168493</v>
@@ -1023,27 +1075,27 @@
         <v>34.46</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:27">
       <c r="A6">
         <v>203</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6">
         <v>2025</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>75</v>
-      </c>
-      <c r="G6">
-        <v>44855</v>
+        <v>76</v>
+      </c>
+      <c r="G6" t="s">
+        <v>82</v>
       </c>
       <c r="H6">
         <v>160407</v>
@@ -1103,27 +1155,27 @@
         <v>41.03</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:27">
       <c r="A7">
         <v>204</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7">
         <v>2025</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>75</v>
-      </c>
-      <c r="G7">
-        <v>45079</v>
+        <v>76</v>
+      </c>
+      <c r="G7" s="2">
+        <v>44963</v>
       </c>
       <c r="H7">
         <v>136426</v>
@@ -1183,27 +1235,27 @@
         <v>22.25</v>
       </c>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:27">
       <c r="A8">
         <v>205</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <v>2025</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>75</v>
-      </c>
-      <c r="G8">
-        <v>45216</v>
+        <v>76</v>
+      </c>
+      <c r="G8" t="s">
+        <v>83</v>
       </c>
       <c r="H8">
         <v>92163</v>
@@ -1263,27 +1315,27 @@
         <v>16.26</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:27">
       <c r="A9">
         <v>206</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9">
         <v>2025</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>75</v>
-      </c>
-      <c r="G9">
-        <v>43524</v>
+        <v>76</v>
+      </c>
+      <c r="G9" t="s">
+        <v>84</v>
       </c>
       <c r="H9">
         <v>177615</v>
@@ -1343,27 +1395,27 @@
         <v>50.9</v>
       </c>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:27">
       <c r="A10">
         <v>207</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10">
         <v>2025</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>75</v>
-      </c>
-      <c r="G10">
-        <v>43787</v>
+        <v>76</v>
+      </c>
+      <c r="G10" t="s">
+        <v>85</v>
       </c>
       <c r="H10">
         <v>93313</v>
@@ -1423,27 +1475,27 @@
         <v>53.69</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:27">
       <c r="A11">
         <v>208</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>2025</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>75</v>
-      </c>
-      <c r="G11">
-        <v>43617</v>
+        <v>76</v>
+      </c>
+      <c r="G11" s="2">
+        <v>43471</v>
       </c>
       <c r="H11">
         <v>179302</v>
@@ -1503,27 +1555,27 @@
         <v>47.77</v>
       </c>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:27">
       <c r="A12">
         <v>209</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>2025</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>75</v>
-      </c>
-      <c r="G12">
-        <v>44494</v>
+        <v>76</v>
+      </c>
+      <c r="G12" t="s">
+        <v>86</v>
       </c>
       <c r="H12">
         <v>61401</v>
@@ -1583,27 +1635,27 @@
         <v>51.5</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:27">
       <c r="A13">
         <v>210</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13">
         <v>2025</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>75</v>
-      </c>
-      <c r="G13">
-        <v>45715</v>
+        <v>76</v>
+      </c>
+      <c r="G13" t="s">
+        <v>87</v>
       </c>
       <c r="H13">
         <v>14303</v>
@@ -1663,27 +1715,27 @@
         <v>26.57</v>
       </c>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:27">
       <c r="A14">
         <v>211</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14">
         <v>2025</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>75</v>
-      </c>
-      <c r="G14">
-        <v>45715</v>
+        <v>76</v>
+      </c>
+      <c r="G14" t="s">
+        <v>87</v>
       </c>
       <c r="H14">
         <v>14640</v>
@@ -1743,27 +1795,27 @@
         <v>35.46</v>
       </c>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:27">
       <c r="A15">
         <v>212</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15">
         <v>2025</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" t="s">
-        <v>76</v>
-      </c>
-      <c r="G15">
-        <v>45520</v>
+        <v>77</v>
+      </c>
+      <c r="G15" t="s">
+        <v>88</v>
       </c>
       <c r="H15">
         <v>54975</v>
@@ -1823,27 +1875,27 @@
         <v>25.06</v>
       </c>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:27">
       <c r="A16">
         <v>213</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16">
         <v>2025</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F16" t="s">
-        <v>77</v>
-      </c>
-      <c r="G16">
-        <v>45510</v>
+        <v>78</v>
+      </c>
+      <c r="G16" s="2">
+        <v>45451</v>
       </c>
       <c r="H16">
         <v>31981</v>
@@ -1908,22 +1960,22 @@
         <v>214</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>2025</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s">
-        <v>77</v>
-      </c>
-      <c r="G17">
-        <v>45510</v>
+        <v>78</v>
+      </c>
+      <c r="G17" s="2">
+        <v>45451</v>
       </c>
       <c r="H17">
         <v>26306</v>
@@ -1988,22 +2040,22 @@
         <v>215</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D18">
         <v>2025</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>77</v>
-      </c>
-      <c r="G18">
-        <v>45502</v>
+        <v>78</v>
+      </c>
+      <c r="G18" t="s">
+        <v>89</v>
       </c>
       <c r="H18">
         <v>20668</v>
@@ -2068,22 +2120,22 @@
         <v>216</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19">
         <v>2025</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F19" t="s">
-        <v>77</v>
-      </c>
-      <c r="G19">
-        <v>45507</v>
+        <v>78</v>
+      </c>
+      <c r="G19" s="2">
+        <v>45359</v>
       </c>
       <c r="H19">
         <v>17639</v>
@@ -2148,22 +2200,22 @@
         <v>217</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D20">
         <v>2025</v>
       </c>
       <c r="E20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F20" t="s">
-        <v>77</v>
-      </c>
-      <c r="G20">
-        <v>45499</v>
+        <v>78</v>
+      </c>
+      <c r="G20" t="s">
+        <v>90</v>
       </c>
       <c r="H20">
         <v>16525</v>
@@ -2228,22 +2280,22 @@
         <v>218</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21">
         <v>2025</v>
       </c>
       <c r="E21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F21" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G21" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="H21">
         <v>241697</v>
@@ -2308,22 +2360,22 @@
         <v>219</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D22">
         <v>2025</v>
       </c>
       <c r="E22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F22" t="s">
-        <v>79</v>
-      </c>
-      <c r="G22">
-        <v>44722</v>
+        <v>80</v>
+      </c>
+      <c r="G22" s="2">
+        <v>44840</v>
       </c>
       <c r="H22">
         <v>48670</v>
@@ -2388,22 +2440,22 @@
         <v>220</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D23">
         <v>2025</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F23" t="s">
-        <v>79</v>
-      </c>
-      <c r="G23">
-        <v>44722</v>
+        <v>80</v>
+      </c>
+      <c r="G23" s="2">
+        <v>44840</v>
       </c>
       <c r="H23">
         <v>62426</v>
@@ -2468,22 +2520,22 @@
         <v>221</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D24">
         <v>2025</v>
       </c>
       <c r="E24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F24" t="s">
-        <v>79</v>
-      </c>
-      <c r="G24">
-        <v>44722</v>
+        <v>80</v>
+      </c>
+      <c r="G24" s="2">
+        <v>44840</v>
       </c>
       <c r="H24">
         <v>54731</v>
@@ -2548,22 +2600,22 @@
         <v>222</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D25">
         <v>2025</v>
       </c>
       <c r="E25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F25" t="s">
-        <v>79</v>
-      </c>
-      <c r="G25">
-        <v>44722</v>
+        <v>80</v>
+      </c>
+      <c r="G25" s="2">
+        <v>44840</v>
       </c>
       <c r="H25">
         <v>55225</v>
@@ -2628,22 +2680,22 @@
         <v>223</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D26">
         <v>2025</v>
       </c>
       <c r="E26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F26" t="s">
-        <v>79</v>
-      </c>
-      <c r="G26">
-        <v>44722</v>
+        <v>80</v>
+      </c>
+      <c r="G26" s="2">
+        <v>44840</v>
       </c>
       <c r="H26">
         <v>54217</v>
@@ -2708,22 +2760,22 @@
         <v>224</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D27">
         <v>2025</v>
       </c>
       <c r="E27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F27" t="s">
-        <v>79</v>
-      </c>
-      <c r="G27">
-        <v>44740</v>
+        <v>80</v>
+      </c>
+      <c r="G27" t="s">
+        <v>92</v>
       </c>
       <c r="H27">
         <v>68638</v>
@@ -2788,22 +2840,22 @@
         <v>225</v>
       </c>
       <c r="B28" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D28">
         <v>2025</v>
       </c>
       <c r="E28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F28" t="s">
-        <v>79</v>
-      </c>
-      <c r="G28">
-        <v>44740</v>
+        <v>80</v>
+      </c>
+      <c r="G28" t="s">
+        <v>92</v>
       </c>
       <c r="H28">
         <v>62910</v>
@@ -2868,22 +2920,22 @@
         <v>226</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D29">
         <v>2025</v>
       </c>
       <c r="E29" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F29" t="s">
-        <v>79</v>
-      </c>
-      <c r="G29">
-        <v>44740</v>
+        <v>80</v>
+      </c>
+      <c r="G29" t="s">
+        <v>92</v>
       </c>
       <c r="H29">
         <v>53000</v>
@@ -2948,21 +3000,21 @@
         <v>227</v>
       </c>
       <c r="B30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C30" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D30">
         <v>2025</v>
       </c>
       <c r="E30" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F30" t="s">
-        <v>79</v>
-      </c>
-      <c r="G30">
+        <v>80</v>
+      </c>
+      <c r="G30" s="2">
         <v>44749</v>
       </c>
       <c r="H30">
@@ -3028,21 +3080,21 @@
         <v>228</v>
       </c>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C31" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D31">
         <v>2025</v>
       </c>
       <c r="E31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F31" t="s">
-        <v>79</v>
-      </c>
-      <c r="G31">
+        <v>80</v>
+      </c>
+      <c r="G31" s="2">
         <v>44749</v>
       </c>
       <c r="H31">
@@ -3108,21 +3160,21 @@
         <v>229</v>
       </c>
       <c r="B32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D32">
         <v>2025</v>
       </c>
       <c r="E32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F32" t="s">
-        <v>79</v>
-      </c>
-      <c r="G32">
+        <v>80</v>
+      </c>
+      <c r="G32" s="2">
         <v>44749</v>
       </c>
       <c r="H32">
@@ -3188,21 +3240,21 @@
         <v>230</v>
       </c>
       <c r="B33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C33" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D33">
         <v>2025</v>
       </c>
       <c r="E33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F33" t="s">
-        <v>79</v>
-      </c>
-      <c r="G33">
+        <v>80</v>
+      </c>
+      <c r="G33" s="2">
         <v>44749</v>
       </c>
       <c r="H33">
@@ -3268,21 +3320,21 @@
         <v>231</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C34" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D34">
         <v>2025</v>
       </c>
       <c r="E34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F34" t="s">
-        <v>79</v>
-      </c>
-      <c r="G34">
+        <v>80</v>
+      </c>
+      <c r="G34" s="2">
         <v>44749</v>
       </c>
       <c r="H34">
@@ -3348,21 +3400,21 @@
         <v>232</v>
       </c>
       <c r="B35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D35">
         <v>2025</v>
       </c>
       <c r="E35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F35" t="s">
-        <v>79</v>
-      </c>
-      <c r="G35">
+        <v>80</v>
+      </c>
+      <c r="G35" s="2">
         <v>44749</v>
       </c>
       <c r="H35">
@@ -3428,21 +3480,21 @@
         <v>233</v>
       </c>
       <c r="B36" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C36" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D36">
         <v>2025</v>
       </c>
       <c r="E36" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F36" t="s">
-        <v>79</v>
-      </c>
-      <c r="G36">
+        <v>80</v>
+      </c>
+      <c r="G36" s="2">
         <v>44749</v>
       </c>
       <c r="H36">
@@ -3508,21 +3560,21 @@
         <v>234</v>
       </c>
       <c r="B37" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C37" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D37">
         <v>2025</v>
       </c>
       <c r="E37" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F37" t="s">
-        <v>79</v>
-      </c>
-      <c r="G37">
+        <v>80</v>
+      </c>
+      <c r="G37" s="2">
         <v>44749</v>
       </c>
       <c r="H37">
@@ -3588,21 +3640,21 @@
         <v>235</v>
       </c>
       <c r="B38" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C38" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D38">
         <v>2025</v>
       </c>
       <c r="E38" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F38" t="s">
-        <v>79</v>
-      </c>
-      <c r="G38">
+        <v>80</v>
+      </c>
+      <c r="G38" s="2">
         <v>44749</v>
       </c>
       <c r="H38">
@@ -3668,21 +3720,21 @@
         <v>236</v>
       </c>
       <c r="B39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C39" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D39">
         <v>2025</v>
       </c>
       <c r="E39" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F39" t="s">
-        <v>79</v>
-      </c>
-      <c r="G39">
+        <v>80</v>
+      </c>
+      <c r="G39" s="2">
         <v>44749</v>
       </c>
       <c r="H39">
@@ -3748,22 +3800,22 @@
         <v>237</v>
       </c>
       <c r="B40" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C40" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D40">
         <v>2025</v>
       </c>
       <c r="E40" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F40" t="s">
-        <v>79</v>
-      </c>
-      <c r="G40">
-        <v>44755</v>
+        <v>80</v>
+      </c>
+      <c r="G40" t="s">
+        <v>93</v>
       </c>
       <c r="H40">
         <v>44630</v>
@@ -3828,22 +3880,22 @@
         <v>238</v>
       </c>
       <c r="B41" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C41" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D41">
         <v>2025</v>
       </c>
       <c r="E41" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F41" t="s">
-        <v>79</v>
-      </c>
-      <c r="G41">
-        <v>44755</v>
+        <v>80</v>
+      </c>
+      <c r="G41" t="s">
+        <v>93</v>
       </c>
       <c r="H41">
         <v>42800</v>
@@ -3908,22 +3960,22 @@
         <v>239</v>
       </c>
       <c r="B42" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C42" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D42">
         <v>2025</v>
       </c>
       <c r="E42" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F42" t="s">
-        <v>79</v>
-      </c>
-      <c r="G42">
-        <v>45072</v>
+        <v>80</v>
+      </c>
+      <c r="G42" t="s">
+        <v>94</v>
       </c>
       <c r="H42">
         <v>26853</v>
@@ -3988,22 +4040,22 @@
         <v>240</v>
       </c>
       <c r="B43" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C43" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D43">
         <v>2025</v>
       </c>
       <c r="E43" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F43" t="s">
-        <v>79</v>
-      </c>
-      <c r="G43">
-        <v>44991</v>
+        <v>80</v>
+      </c>
+      <c r="G43" s="2">
+        <v>45080</v>
       </c>
       <c r="H43">
         <v>56980</v>
@@ -4068,22 +4120,22 @@
         <v>241</v>
       </c>
       <c r="B44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C44" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D44">
         <v>2025</v>
       </c>
       <c r="E44" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F44" t="s">
-        <v>79</v>
-      </c>
-      <c r="G44">
-        <v>45072</v>
+        <v>80</v>
+      </c>
+      <c r="G44" t="s">
+        <v>94</v>
       </c>
       <c r="H44">
         <v>55853</v>
@@ -4148,22 +4200,22 @@
         <v>242</v>
       </c>
       <c r="B45" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C45" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D45">
         <v>2025</v>
       </c>
       <c r="E45" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F45" t="s">
         <v>80</v>
       </c>
-      <c r="G45">
-        <v>45625</v>
+      <c r="G45" t="s">
+        <v>95</v>
       </c>
       <c r="H45">
         <v>15909</v>
@@ -4228,22 +4280,22 @@
         <v>243</v>
       </c>
       <c r="B46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C46" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D46">
         <v>2025</v>
       </c>
       <c r="E46" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F46" t="s">
         <v>80</v>
       </c>
-      <c r="G46">
-        <v>45625</v>
+      <c r="G46" t="s">
+        <v>95</v>
       </c>
       <c r="H46">
         <v>52704</v>
@@ -4308,22 +4360,22 @@
         <v>244</v>
       </c>
       <c r="B47" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C47" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D47">
         <v>2025</v>
       </c>
       <c r="E47" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F47" t="s">
         <v>80</v>
       </c>
-      <c r="G47">
-        <v>45804</v>
+      <c r="G47" t="s">
+        <v>96</v>
       </c>
       <c r="H47">
         <v>165</v>
@@ -4388,22 +4440,22 @@
         <v>245</v>
       </c>
       <c r="B48" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C48" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D48">
         <v>2025</v>
       </c>
       <c r="E48" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F48" t="s">
         <v>81</v>
       </c>
-      <c r="G48">
-        <v>45681</v>
+      <c r="G48" t="s">
+        <v>97</v>
       </c>
       <c r="H48">
         <v>720</v>
